--- a/Result/profitability/5703.xlsx
+++ b/Result/profitability/5703.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1</v>
+        <v>0.14125</v>
       </c>
       <c r="N2" t="n">
-        <v>44.02625</v>
+        <v>47.0775</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1125</v>
+        <v>0.09250000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>48.79625</v>
+        <v>48.1925</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04125000000000001</v>
+        <v>0.04250000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>49.4175</v>
+        <v>49.6925</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.38</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.15</v>
+        <v>-0.1275</v>
       </c>
       <c r="N5" t="n">
-        <v>51.04</v>
+        <v>52.09875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.23</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.17625</v>
+        <v>-0.15</v>
       </c>
       <c r="N6" t="n">
-        <v>53.45500000000001</v>
+        <v>55.14875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.17</v>
+        <v>-0.205</v>
       </c>
       <c r="N7" t="n">
-        <v>56.80625</v>
+        <v>55.69</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.11</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.23875</v>
+        <v>-0.2524999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>57.1375</v>
+        <v>56.79</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2030,7 +2030,7 @@
         <v>0.14</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0775</v>
+        <v>0.07750000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>61.87875</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5703</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>118</v>
+      </c>
+      <c r="D75" t="n">
+        <v>63</v>
+      </c>
+      <c r="E75" t="n">
+        <v>54</v>
+      </c>
+      <c r="F75" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="G75" t="n">
+        <v>13</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.73%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>14</v>
+      </c>
+      <c r="K75" t="n">
+        <v>11</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>42.12875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4074074074074074</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.780000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0568274734260017</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.469999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2248473586408282</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
